--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -4976,8 +4976,16 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>已测试：品牌管理员可选择多门店</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -7743,8 +7751,16 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>已测试：显示适用门店列表</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -9574,10 +9590,14 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>核心多店功能</t>
+          <t>核心多店功能; 已测试：品牌 deal 发布后门店可确认，客户端多门店可见</t>
         </is>
       </c>
     </row>
@@ -9622,8 +9642,16 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>已测试：门店拒绝后客户端不显示该门店</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
